--- a/daily_matches/job_matches_2026-05-23.xlsx
+++ b/daily_matches/job_matches_2026-05-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior ML Ops Engineer</t>
+          <t>Sr. Data Scientist - Industrial Industry Focused</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Cutsforth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, S3, EC2, MLflow, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6329c226be016e1</t>
+          <t>https://www.indeed.com/viewjob?jk=eddc02446663baaf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI ML Engineer</t>
+          <t>Senior AWS/Cloud Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, XGBoost, S3, BigQuery, Dataflow, Docker</t>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3d1643e35a4371</t>
+          <t>https://www.indeed.com/viewjob?jk=d873fd036d4ccc32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Machine Learning Engineering Consultant (Hybrid)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, TensorFlow, PyTorch, XGBoost, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ebea37145761f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d1acf62fe8826b5c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70861cab09f5e001</t>
+          <t>https://www.indeed.com/viewjob?jk=030126450e418acf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7a803b7840ea2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b24c09f7e673d0e5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ccd5760cf35ff89</t>
+          <t>https://www.indeed.com/viewjob?jk=e52dead841965820</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d64ee153e7a0aa1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0e7fbdacc0e968</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Invoca</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, spaCy, Data Lake, MLflow, Kubernetes, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73e8fd2c508a14c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab1721b38b391cf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer (Onsite Hybrid)</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, Glue, Data Lake, Terraform, Git, Snowflake, Kafka, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=497592bce61ae348</t>
+          <t>https://www.indeed.com/viewjob?jk=d26cd3e37251004e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7681e7d24e6f7a34</t>
+          <t>https://www.indeed.com/viewjob?jk=c222add675bbff72</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a29cd937a4a7667</t>
+          <t>https://www.indeed.com/viewjob?jk=61a1dee23a8579cd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adedb51b7a8a32c6</t>
+          <t>https://www.indeed.com/viewjob?jk=2146075cee737893</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43a63e7e6f41601</t>
+          <t>https://www.indeed.com/viewjob?jk=772cac77cd7ef2d4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e53cb1d6c5afda41</t>
+          <t>https://www.indeed.com/viewjob?jk=9e174af62b520be7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Birmingham, MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, Kafka, MongoDB, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44fdf2eafecdc57a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ab4d772ab64022</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Systems</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5d99a3a7854f4d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b31a4822c2fd7ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Energy, Sales, &amp; Services</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kafka, MySQL, MongoDB, NoSQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3666b5644b9c9923</t>
+          <t>https://www.indeed.com/viewjob?jk=72f14153c95a3108</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfad6c83544ca38a</t>
+          <t>https://www.indeed.com/viewjob?jk=8d300d322ff775bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Greetings</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westlake, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Copilot, Git, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54f88233421570fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4799fb0cb3cd63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeta Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f91bfeb4770ab660</t>
+          <t>https://www.indeed.com/viewjob?jk=175ada5f372a9a1c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8d66f444cfbb33</t>
+          <t>https://www.indeed.com/viewjob?jk=78042687e4a5d244</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28722c45af0241a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce7bdec21ac8933</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer, AI &amp; Automation</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484fde89bf366602</t>
+          <t>https://www.indeed.com/viewjob?jk=9869233d98130163</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer, AI &amp; Automation</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Customers Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af44a2edb4f866bb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6c30ddd0431063</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Wireless Systems Software</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba69ca95a884b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=51a0a98612ec818b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Paramount Streaming</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,42 +1371,7147 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a47b0f5fae45e8e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a1003fe1400cee1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Science</t>
+          <t>Senior Data Scientist - SFL Scientific</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPS Services, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7b34853426f255f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d265e3b62d9f39ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54c412b3055ae086</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37da970141082d87</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0313be2e3087c19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ec1a9a7ede46b98</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dfba180c9875a09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=967b066f98f4eb81</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f58f9a1e842d1fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5d1cc42d6d9cb6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4241b7ae3a774a86</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e1acb234a3e31d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - SFL Scientific</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b169a169c9deeb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, BigQuery, CI/CD, Terraform, Git, BigQuery, Matplotlib, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df7632bc7852179f</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Relayer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Wayne, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Pinecone, BigQuery, Git, Snowflake, BigQuery, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6ece019a4134137</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>The Goal Family of Companies</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0903726c2a50be0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cloud Engineer - Project Delivery Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b009b8ae81c7333</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=042473cbbc55d6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ecf623fa9129410</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b50b009f71d627c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee6a95bc561c4902</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=093e6c10a2c057a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2ebf8ed9b7cb73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a89a64a00b752b2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db1376e0a8de8d3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbc1964846123708</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0091e54edea06039</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aab9aa1ffee316ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13942439b2fc6499</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd9c29bd0cba4b4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de636330358084a</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0af072b3dbc20d63</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04742123fc853ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c57f70ed2ba94d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ea0b61d37496042</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Finance Analytics &amp; AI Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Gemini, TensorFlow, PyTorch, Snowflake, Databricks, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d313c54993bd2c7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60ae27f185576a85</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DATA ENGINEER II</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sony Pictures Entertainment</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Culver City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=582ab9e97ccf598f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22f5301864ffcc6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c44ebebf97995a8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb5291f2e0930e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4af953382504d0a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dec622f2dd67bb96</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1269e9582d723219</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69a29605d144341c</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=025b69b3c1746c86</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34ecd0eeeb36006a</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0a6ef2871fad72a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6eab8e428efd0e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=852c4cb6e2a10919</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dacbf2302adfbf05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a189cae1734d076</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7774ee50513b7463</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fefefb4dcd709c7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7a4df7baee3e3af</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c51e48ce42389ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a56919353500960</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68cfbc58c6641813</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecfab588e5cf6c29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42c03dcdb2848a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9839dedf263b90d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93dfb268203339cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e57571c605e5734b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=244910e34bce9ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b41ef1211ec86e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2b3d96e0a8e21ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8556e2a11538256a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e09f9f4ad5ab03ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=089e5232da1ecc19</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f79ec4b5877ff0ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b42835caa2e86bda</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d29d534bf1673ea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f486f7bf3ed634eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cac1bfd092152d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76831a6545fcf5c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45de8b9888696a5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1fd2098ef563938</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3569c0efcfdb20d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Jericho, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=160779e610d1757d</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f25ea27b6fb91243</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b81cfb10d618b1f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9845ac9347983473</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b1fd679a1cb95c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99e4d00a62ecc904</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04ce05bf84c4d460</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0dce4712225bcccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f42deeeef988a27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a547bdd0ccc5a4b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612e931b11ff6427</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Cyber Full-Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Docker, Kubernetes, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f13e48975e8957b</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Engineering Enablement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ba0dd7cb1f377ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Solutions Architect - Digital Systems</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Formlabs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad04864d86b9cf43</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f4b5f508883ddae</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25c0b5a822108fd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a06e479c1c3b9f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94adf005a70a8673</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55396b0cce5f7377</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fb9bb4cb2d5a2ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fa6444ccb5085f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b671313fff8cc4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38650208ea08126b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca34c6a40c50ffdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a12f9bd497a1d953</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=935a2d0c89d80621</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=372569a48213b812</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c1bc6ef3cbdea</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95523bc82ec7453</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00c5d32b2034722b</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c17f45cd7268ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=737281ec21e60a50</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b72fcd80a1026cd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Consultant - Data Science / Data Lake</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, Data Lake, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5e1ba2a4c21a7cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, FastAPI, CI/CD, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7135ede7ebcf2d99</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Software Engineer 2</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79df895a2c776097</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Solutions Analyst</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652d1607a6e764a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=091cca92729e73c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a97660457b6a704</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccdd565e2ce480e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a328d24f90bffc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d2beb6639d57259</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30e42d392d36915a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6805ec7f4b2164a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce9d3046430947b</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59a3963686140642</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9940d5f6dd9d7849</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41461490c06755ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=538f4712ab5f9882</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce9a8447a4594b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6ae9b8e3be14d79</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed6912c00d0f4c5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3897d21bb82d99b</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f98bac1f38f07d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd5b591e7993d452</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784249a82ca5026a</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39812d26590ea0ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38d0033470d170a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0832ae59c87eed90</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8dd1a3558bbbfbd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eff529fa73fe3c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee6dc510af009d9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5ca83bd7322a8c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b463fa9e9c1c41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e006765da2179d96</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00fad58868166eb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94cb3ca03890de86</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=840636ce22b6f4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff0c830da48724e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce862bc017c15dcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a04eb69f5c20c4b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8e8d0ce34ca6f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=993d159a1eb3a584</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fc46bbc71465c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e5c7e752590747e</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fd8c97052fbde2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54e21a97fc7dc8ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Physical and Spatial AI Architect</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, TensorFlow, Kubernetes, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f00683022fd43aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Data Engineer 2 - Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Tableau, Python, SQL, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1db5f2ff1d0e94db</t>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, BigQuery, Kafka, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7805bc28c8fdf866</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Swire Coca-Cola</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0435888f6ae1c7be</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Swire Coca-Cola</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44918515cc924cb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Senior Engineer ML Apps</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>VITRO</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Cheswick, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, FastAPI, Docker, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e1259e011b1e68</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5eb50ea19d98c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=576d5b428087cdc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=315d3f204fc9e8e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=424c7cc37a8a6678</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25facd0e218bcbe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7554a94d3338b0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5881189f492c9a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c6c74b9bbec2a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3951e2243912655</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=114bb4b566664228</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39bb50624ef655d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc04f0e8899b977a</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70beaf8fcea77a84</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50d2d279582183c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccfb3ef0a549c08d</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5b243d69ef68250</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>San Juan, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=491b11a362fe05ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adaa60de46054a1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59157ea35d02e776</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eec1594f8c94a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58fc8fa9e0bec3cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18af3fdeaabfbb4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dee7d24ad5488c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccd98790f4dc27ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7f8ea9a72af8412</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=809b1440ad629f76</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31417c4ebcfc757a</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=261047b348a3bc9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>10</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d0176715238c975</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>10</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2ac9a8147bf96e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6476081914f79e68</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0c84441fb6738e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a841ed24ebbda11</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>10</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abc24d431ec6cd5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>10</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bb89dbd70712e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=790490ccbfeb5bcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90b325523862267a</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>10</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f85c5b6503a14db0</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>10</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63dc5f4fde52ff47</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>10</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c3b5321f529d5ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>10</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c4cb19059726c43</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>10</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c4c20736647fdf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>10</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=954d07fe5c3da51b</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Pricing Advisor</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>10</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2090dab960406f88</t>
         </is>
       </c>
     </row>
